--- a/inputs/AddictO_Human_behaviour_Defs.xlsx
+++ b/inputs/AddictO_Human_behaviour_Defs.xlsx
@@ -683,65 +683,65 @@
       <c r="U3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000102</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>abrupt smoking cessation</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Smoking cessation in which a smoker goes from his or her usual level of cigarette consumption to no use of cigarette within a day.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">cigarette cessation </t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Occurrent</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="n">
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr"/>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -937,65 +937,65 @@
       <c r="U7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000106</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>accidental smoking cessation</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Smoking cessation that occurs without a smoker having an intention to stop smoking.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">cigarette cessation </t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="n">
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3641,63 +3641,63 @@
       <c r="U55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000632</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>cannabis use</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>A cannabis use behaviour that involves ingesting cannabis.</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>product use behaviour</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr"/>
+      <c r="R56" s="7" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr"/>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T56" s="7" t="inlineStr"/>
+      <c r="U56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr"/>
@@ -4745,138 +4745,138 @@
       <c r="U75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000646</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>cigarette purchase behaviour</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>A product purchase behaviour in which the product is some cigarettes.</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Buying cigarettes.</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>purchase behaviour</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>dependent continuant</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tobacco purchase </t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr"/>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="3" t="inlineStr"/>
-      <c r="O76" s="3" t="n">
+      <c r="L76" s="7" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr"/>
+      <c r="O76" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P76" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q76" s="3" t="inlineStr"/>
-      <c r="R76" s="3" t="inlineStr">
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr"/>
+      <c r="R76" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S76" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T76" s="3" t="inlineStr"/>
-      <c r="U76" s="3" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T76" s="7" t="inlineStr"/>
+      <c r="U76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000640</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>cigarette smoking</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour pattern that involves ingesting smoke from a cigarette.</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
-      <c r="K77" s="3" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>Tobacco smoking</t>
         </is>
       </c>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="3" t="n">
+      <c r="L77" s="7" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P77" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q77" s="3" t="inlineStr"/>
-      <c r="R77" s="3" t="inlineStr">
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr"/>
+      <c r="R77" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S77" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T77" s="3" t="inlineStr"/>
-      <c r="U77" s="3" t="inlineStr"/>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T77" s="7" t="inlineStr"/>
+      <c r="U77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -7363,69 +7363,69 @@
       <c r="U128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000660</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>dual cigarette and smokeless tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour pattern that involves the use of combustible tobacco and smokeless tobacco.</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="3" t="inlineStr"/>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr"/>
+      <c r="E129" s="7" t="inlineStr"/>
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="G129" s="7" t="inlineStr">
         <is>
           <t>process aggregate</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
-      <c r="K129" s="3" t="inlineStr">
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr">
         <is>
           <t>Dual use</t>
         </is>
       </c>
-      <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="3" t="inlineStr"/>
-      <c r="N129" s="3" t="inlineStr"/>
-      <c r="O129" s="3" t="n">
+      <c r="L129" s="7" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+      <c r="N129" s="7" t="inlineStr"/>
+      <c r="O129" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P129" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q129" s="3" t="inlineStr"/>
-      <c r="R129" s="3" t="inlineStr">
+      <c r="P129" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q129" s="7" t="inlineStr"/>
+      <c r="R129" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S129" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T129" s="3" t="inlineStr"/>
-      <c r="U129" s="3" t="inlineStr"/>
+      <c r="S129" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T129" s="7" t="inlineStr"/>
+      <c r="U129" s="7" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8243,130 +8243,130 @@
       <c r="U142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000674</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>e-cigarette puff</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>A behavioural episode that involves the act of drawing aerosol produced by an e-cigarette into the body.</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr"/>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>e-cigarette use</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" s="7" t="inlineStr">
         <is>
           <t>Dependent continuant</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr"/>
-      <c r="O143" s="2" t="n">
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr"/>
+      <c r="K143" s="7" t="inlineStr"/>
+      <c r="L143" s="7" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+      <c r="N143" s="7" t="inlineStr"/>
+      <c r="O143" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P143" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q143" s="2" t="inlineStr"/>
-      <c r="R143" s="2" t="inlineStr">
+      <c r="P143" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q143" s="7" t="inlineStr"/>
+      <c r="R143" s="7" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="S143" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T143" s="2" t="inlineStr"/>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="S143" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T143" s="7" t="inlineStr"/>
+      <c r="U143" s="7" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000673</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>e-cigarette purchase behaviour</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>A product purchase in which the product is an e-cigarette.</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr"/>
-      <c r="E144" s="3" t="inlineStr"/>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr">
         <is>
           <t>purchase behaviour</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>dependent continuant</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr"/>
-      <c r="J144" s="3" t="inlineStr"/>
-      <c r="K144" s="3" t="inlineStr">
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr"/>
+      <c r="J144" s="7" t="inlineStr"/>
+      <c r="K144" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">E-cigarette purchase </t>
         </is>
       </c>
-      <c r="L144" s="3" t="inlineStr"/>
-      <c r="M144" s="3" t="inlineStr"/>
-      <c r="N144" s="3" t="inlineStr"/>
-      <c r="O144" s="3" t="n">
+      <c r="L144" s="7" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+      <c r="N144" s="7" t="inlineStr"/>
+      <c r="O144" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P144" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q144" s="3" t="inlineStr"/>
-      <c r="R144" s="3" t="inlineStr">
+      <c r="P144" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q144" s="7" t="inlineStr"/>
+      <c r="R144" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S144" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T144" s="3" t="inlineStr"/>
-      <c r="U144" s="3" t="inlineStr"/>
+      <c r="S144" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T144" s="7" t="inlineStr"/>
+      <c r="U144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
@@ -9186,73 +9186,73 @@
       <c r="U159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000677</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" s="7" t="inlineStr">
         <is>
           <t>experimentation with e-cigarettes</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" s="7" t="inlineStr">
         <is>
           <t>An e-cigarette use behaviour which indicates the trial use of e-cigarette devices.</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D160" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Trial use of an e-cigarette without frequent or committed usage. </t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="E160" s="7" t="inlineStr"/>
+      <c r="F160" s="7" t="inlineStr">
         <is>
           <t>e-cigarette use</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
         <is>
           <t>Dependent continuant</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr">
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="inlineStr"/>
+      <c r="J160" s="7" t="inlineStr"/>
+      <c r="K160" s="7" t="inlineStr"/>
+      <c r="L160" s="7" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">People may experiment with when they first encounter e-cigarettes but not all will go on to become regular users. </t>
         </is>
       </c>
-      <c r="N160" s="2" t="inlineStr"/>
-      <c r="O160" s="2" t="n">
+      <c r="N160" s="7" t="inlineStr"/>
+      <c r="O160" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P160" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q160" s="2" t="inlineStr"/>
-      <c r="R160" s="2" t="inlineStr">
+      <c r="P160" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q160" s="7" t="inlineStr"/>
+      <c r="R160" s="7" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="S160" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T160" s="2" t="inlineStr"/>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="S160" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T160" s="7" t="inlineStr"/>
+      <c r="U160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr"/>
@@ -9705,61 +9705,61 @@
       <c r="U170" s="7" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000678</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" s="7" t="inlineStr">
         <is>
           <t>gradual smoking cessation</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>Smoking cessation in which a smoker goes from his or her usual level of cigarette consumption to no use of cigarette over a period of time.</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="D171" s="7" t="inlineStr"/>
+      <c r="E171" s="7" t="inlineStr"/>
+      <c r="F171" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">cigarette cessation </t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="2" t="inlineStr"/>
-      <c r="M171" s="2" t="inlineStr"/>
-      <c r="N171" s="2" t="inlineStr"/>
-      <c r="O171" s="2" t="n">
+      <c r="G171" s="7" t="inlineStr"/>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr"/>
+      <c r="K171" s="7" t="inlineStr"/>
+      <c r="L171" s="7" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+      <c r="N171" s="7" t="inlineStr"/>
+      <c r="O171" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P171" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q171" s="2" t="inlineStr"/>
-      <c r="R171" s="2" t="inlineStr">
+      <c r="P171" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q171" s="7" t="inlineStr"/>
+      <c r="R171" s="7" t="inlineStr">
         <is>
           <t>SC; JH</t>
         </is>
       </c>
-      <c r="S171" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T171" s="2" t="inlineStr"/>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="S171" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T171" s="7" t="inlineStr"/>
+      <c r="U171" s="7" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr"/>
@@ -10748,189 +10748,189 @@
       <c r="U189" s="7" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000981</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>heated tobacco containing product use</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour that involves using a heated tobacco containing product.</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr"/>
-      <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="D190" s="7" t="inlineStr"/>
+      <c r="E190" s="7" t="inlineStr"/>
+      <c r="F190" s="7" t="inlineStr">
         <is>
           <t>product use behaviour</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="2" t="inlineStr"/>
-      <c r="N190" s="2" t="inlineStr"/>
-      <c r="O190" s="2" t="n">
+      <c r="G190" s="7" t="inlineStr"/>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="inlineStr"/>
+      <c r="J190" s="7" t="inlineStr"/>
+      <c r="K190" s="7" t="inlineStr"/>
+      <c r="L190" s="7" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+      <c r="N190" s="7" t="inlineStr"/>
+      <c r="O190" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P190" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q190" s="2" t="inlineStr"/>
-      <c r="R190" s="2" t="inlineStr">
+      <c r="P190" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q190" s="7" t="inlineStr"/>
+      <c r="R190" s="7" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="S190" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T190" s="2" t="inlineStr"/>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="S190" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T190" s="7" t="inlineStr"/>
+      <c r="U190" s="7" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000687</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>heated tobacco-containing product purchase behaviour</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A product purchase in which the product is a heated tobacco containing product. </t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr"/>
-      <c r="E191" s="3" t="inlineStr"/>
-      <c r="F191" s="3" t="inlineStr">
+      <c r="D191" s="7" t="inlineStr"/>
+      <c r="E191" s="7" t="inlineStr"/>
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>purchase behaviour</t>
         </is>
       </c>
-      <c r="G191" s="3" t="inlineStr">
+      <c r="G191" s="7" t="inlineStr">
         <is>
           <t>dependent continuant</t>
         </is>
       </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I191" s="3" t="inlineStr"/>
-      <c r="J191" s="3" t="inlineStr"/>
-      <c r="K191" s="3" t="inlineStr">
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="inlineStr"/>
+      <c r="J191" s="7" t="inlineStr"/>
+      <c r="K191" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tobacco purchase </t>
         </is>
       </c>
-      <c r="L191" s="3" t="inlineStr"/>
-      <c r="M191" s="3" t="inlineStr"/>
-      <c r="N191" s="3" t="inlineStr"/>
-      <c r="O191" s="3" t="n">
+      <c r="L191" s="7" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+      <c r="N191" s="7" t="inlineStr"/>
+      <c r="O191" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P191" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q191" s="3" t="inlineStr"/>
-      <c r="R191" s="3" t="inlineStr">
+      <c r="P191" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q191" s="7" t="inlineStr"/>
+      <c r="R191" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S191" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T191" s="3" t="inlineStr"/>
-      <c r="U191" s="3" t="inlineStr"/>
+      <c r="S191" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T191" s="7" t="inlineStr"/>
+      <c r="U191" s="7" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000679</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>heated tobacco-containing product use</t>
         </is>
       </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour pattern that is use of a heated tobacco-containing product.</t>
         </is>
       </c>
-      <c r="D192" s="3" t="inlineStr"/>
-      <c r="E192" s="3" t="inlineStr"/>
-      <c r="F192" s="3" t="inlineStr">
+      <c r="D192" s="7" t="inlineStr"/>
+      <c r="E192" s="7" t="inlineStr"/>
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">tobacco use behaviour pattern </t>
         </is>
       </c>
-      <c r="G192" s="3" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I192" s="3" t="inlineStr"/>
-      <c r="J192" s="3" t="inlineStr"/>
-      <c r="K192" s="3" t="inlineStr"/>
-      <c r="L192" s="3" t="inlineStr"/>
-      <c r="M192" s="3" t="inlineStr"/>
-      <c r="N192" s="3" t="inlineStr"/>
-      <c r="O192" s="3" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="inlineStr"/>
+      <c r="J192" s="7" t="inlineStr"/>
+      <c r="K192" s="7" t="inlineStr"/>
+      <c r="L192" s="7" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+      <c r="N192" s="7" t="inlineStr"/>
+      <c r="O192" s="7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="P192" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q192" s="3" t="inlineStr"/>
-      <c r="R192" s="3" t="inlineStr">
+      <c r="P192" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q192" s="7" t="inlineStr"/>
+      <c r="R192" s="7" t="inlineStr">
         <is>
           <t>KS; RW</t>
         </is>
       </c>
-      <c r="S192" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T192" s="3" t="inlineStr"/>
-      <c r="U192" s="3" t="inlineStr"/>
+      <c r="S192" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T192" s="7" t="inlineStr"/>
+      <c r="U192" s="7" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -15412,65 +15412,65 @@
       <c r="U284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+      <c r="A285" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000628</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
+      <c r="B285" s="7" t="inlineStr">
         <is>
           <t>planned cigarette smoking quit attempt</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
+      <c r="C285" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour where the person plans to quit smoking.</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr"/>
-      <c r="E285" s="2" t="inlineStr"/>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="D285" s="7" t="inlineStr"/>
+      <c r="E285" s="7" t="inlineStr"/>
+      <c r="F285" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">cigarette cessation </t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="G285" s="7" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="H285" s="2" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I285" s="2" t="inlineStr"/>
-      <c r="J285" s="2" t="inlineStr"/>
-      <c r="K285" s="2" t="inlineStr"/>
-      <c r="L285" s="2" t="inlineStr"/>
-      <c r="M285" s="2" t="inlineStr"/>
-      <c r="N285" s="2" t="inlineStr"/>
-      <c r="O285" s="2" t="n">
+      <c r="H285" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I285" s="7" t="inlineStr"/>
+      <c r="J285" s="7" t="inlineStr"/>
+      <c r="K285" s="7" t="inlineStr"/>
+      <c r="L285" s="7" t="inlineStr"/>
+      <c r="M285" s="7" t="inlineStr"/>
+      <c r="N285" s="7" t="inlineStr"/>
+      <c r="O285" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P285" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q285" s="2" t="inlineStr"/>
-      <c r="R285" s="2" t="inlineStr">
+      <c r="P285" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q285" s="7" t="inlineStr"/>
+      <c r="R285" s="7" t="inlineStr">
         <is>
           <t>SC; JH</t>
         </is>
       </c>
-      <c r="S285" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="T285" s="2" t="inlineStr"/>
-      <c r="U285" s="2" t="inlineStr"/>
+      <c r="S285" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T285" s="7" t="inlineStr"/>
+      <c r="U285" s="7" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -19259,69 +19259,69 @@
       <c r="U365" s="7" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="inlineStr">
+      <c r="A366" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000708</t>
         </is>
       </c>
-      <c r="B366" s="3" t="inlineStr">
+      <c r="B366" s="7" t="inlineStr">
         <is>
           <t>smokeless tobacco purchase behaviour</t>
         </is>
       </c>
-      <c r="C366" s="3" t="inlineStr">
+      <c r="C366" s="7" t="inlineStr">
         <is>
           <t>A product purchase in which the product is smokeless tobacco.</t>
         </is>
       </c>
-      <c r="D366" s="3" t="inlineStr"/>
-      <c r="E366" s="3" t="inlineStr"/>
-      <c r="F366" s="3" t="inlineStr">
+      <c r="D366" s="7" t="inlineStr"/>
+      <c r="E366" s="7" t="inlineStr"/>
+      <c r="F366" s="7" t="inlineStr">
         <is>
           <t>purchase behaviour</t>
         </is>
       </c>
-      <c r="G366" s="3" t="inlineStr">
+      <c r="G366" s="7" t="inlineStr">
         <is>
           <t>dependent continuant</t>
         </is>
       </c>
-      <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I366" s="3" t="inlineStr"/>
-      <c r="J366" s="3" t="inlineStr"/>
-      <c r="K366" s="3" t="inlineStr">
+      <c r="H366" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I366" s="7" t="inlineStr"/>
+      <c r="J366" s="7" t="inlineStr"/>
+      <c r="K366" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tobacco purchase </t>
         </is>
       </c>
-      <c r="L366" s="3" t="inlineStr"/>
-      <c r="M366" s="3" t="inlineStr"/>
-      <c r="N366" s="3" t="inlineStr"/>
-      <c r="O366" s="3" t="n">
+      <c r="L366" s="7" t="inlineStr"/>
+      <c r="M366" s="7" t="inlineStr"/>
+      <c r="N366" s="7" t="inlineStr"/>
+      <c r="O366" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P366" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q366" s="3" t="inlineStr"/>
-      <c r="R366" s="3" t="inlineStr">
+      <c r="P366" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q366" s="7" t="inlineStr"/>
+      <c r="R366" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S366" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T366" s="3" t="inlineStr"/>
-      <c r="U366" s="3" t="inlineStr"/>
+      <c r="S366" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T366" s="7" t="inlineStr"/>
+      <c r="U366" s="7" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
@@ -19452,69 +19452,69 @@
       <c r="U368" s="3" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="inlineStr">
+      <c r="A369" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000699</t>
         </is>
       </c>
-      <c r="B369" s="3" t="inlineStr">
+      <c r="B369" s="7" t="inlineStr">
         <is>
           <t>smokeless tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="C369" s="3" t="inlineStr">
+      <c r="C369" s="7" t="inlineStr">
         <is>
           <t>A tobacco use behaviour pattern that involves the use of a smokeless tobacco-containing product.</t>
         </is>
       </c>
-      <c r="D369" s="3" t="inlineStr"/>
-      <c r="E369" s="3" t="inlineStr"/>
-      <c r="F369" s="3" t="inlineStr">
+      <c r="D369" s="7" t="inlineStr"/>
+      <c r="E369" s="7" t="inlineStr"/>
+      <c r="F369" s="7" t="inlineStr">
         <is>
           <t>tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="G369" s="3" t="inlineStr">
+      <c r="G369" s="7" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="H369" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I369" s="3" t="inlineStr"/>
-      <c r="J369" s="3" t="inlineStr"/>
-      <c r="K369" s="3" t="inlineStr">
+      <c r="H369" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I369" s="7" t="inlineStr"/>
+      <c r="J369" s="7" t="inlineStr"/>
+      <c r="K369" s="7" t="inlineStr">
         <is>
           <t>smokeless tobacco use</t>
         </is>
       </c>
-      <c r="L369" s="3" t="inlineStr"/>
-      <c r="M369" s="3" t="inlineStr"/>
-      <c r="N369" s="3" t="inlineStr"/>
-      <c r="O369" s="3" t="n">
+      <c r="L369" s="7" t="inlineStr"/>
+      <c r="M369" s="7" t="inlineStr"/>
+      <c r="N369" s="7" t="inlineStr"/>
+      <c r="O369" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P369" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q369" s="3" t="inlineStr"/>
-      <c r="R369" s="3" t="inlineStr">
+      <c r="P369" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q369" s="7" t="inlineStr"/>
+      <c r="R369" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S369" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T369" s="3" t="inlineStr"/>
-      <c r="U369" s="3" t="inlineStr"/>
+      <c r="S369" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T369" s="7" t="inlineStr"/>
+      <c r="U369" s="7" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">

--- a/inputs/AddictO_Human_behaviour_Defs.xlsx
+++ b/inputs/AddictO_Human_behaviour_Defs.xlsx
@@ -12638,73 +12638,73 @@
       <c r="U228" s="7" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="inlineStr">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t>ADDICTO:0000710</t>
         </is>
       </c>
-      <c r="B229" s="3" t="inlineStr">
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t>non-daily smokeless tobacco use</t>
         </is>
       </c>
-      <c r="C229" s="3" t="inlineStr">
+      <c r="C229" s="7" t="inlineStr">
         <is>
           <t>A smokeless tobacco use behaviour pattern that involves not using smokeless tobacco every day.</t>
         </is>
       </c>
-      <c r="D229" s="3" t="inlineStr"/>
-      <c r="E229" s="3" t="inlineStr"/>
-      <c r="F229" s="3" t="inlineStr">
+      <c r="D229" s="7" t="inlineStr"/>
+      <c r="E229" s="7" t="inlineStr"/>
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>smokeless tobacco use behaviour pattern</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr">
+      <c r="G229" s="7" t="inlineStr">
         <is>
           <t>process aggregate</t>
         </is>
       </c>
-      <c r="H229" s="3" t="inlineStr">
-        <is>
-          <t>Human behaviour</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="inlineStr"/>
-      <c r="J229" s="3" t="inlineStr"/>
-      <c r="K229" s="3" t="inlineStr">
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>Human behaviour</t>
+        </is>
+      </c>
+      <c r="I229" s="7" t="inlineStr"/>
+      <c r="J229" s="7" t="inlineStr"/>
+      <c r="K229" s="7" t="inlineStr">
         <is>
           <t>occasional smokeless tobacco use</t>
         </is>
       </c>
-      <c r="L229" s="3" t="inlineStr"/>
-      <c r="M229" s="3" t="inlineStr">
+      <c r="L229" s="7" t="inlineStr"/>
+      <c r="M229" s="7" t="inlineStr">
         <is>
           <t>The mean frequency of use could be &gt;1 per day but there are days when smokeless tobacco is not used.</t>
         </is>
       </c>
-      <c r="N229" s="3" t="inlineStr"/>
-      <c r="O229" s="3" t="n">
+      <c r="N229" s="7" t="inlineStr"/>
+      <c r="O229" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P229" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q229" s="3" t="inlineStr"/>
-      <c r="R229" s="3" t="inlineStr">
+      <c r="P229" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q229" s="7" t="inlineStr"/>
+      <c r="R229" s="7" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="S229" s="3" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="T229" s="3" t="inlineStr"/>
-      <c r="U229" s="3" t="inlineStr"/>
+      <c r="S229" s="7" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="T229" s="7" t="inlineStr"/>
+      <c r="U229" s="7" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="inlineStr"/>
